--- a/results/Int Task Remove ACC 0.7/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC 0.7/Rando_3_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6167328551838898</v>
+        <v>0.6956304022926521</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6282962651957537</v>
+        <v>0.6956304022926521</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6469048040922608</v>
+        <v>0.6971547925365545</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6530023650678706</v>
+        <v>0.6971547925365545</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6502694405497434</v>
+        <v>0.7144450179498637</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6377584626288462</v>
+        <v>0.7181255103770242</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6091657935688644</v>
+        <v>0.7691035083124047</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6268267645563379</v>
+        <v>0.7691035083124047</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6042767668674792</v>
+        <v>0.7906510484877433</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6042767668674792</v>
+        <v>0.7876022679999384</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6039609108978014</v>
+        <v>0.8313290602899712</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6100584718734111</v>
+        <v>0.7534339706947291</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6310840793183674</v>
+        <v>0.7578559542702187</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6310840793183674</v>
+        <v>0.748709612806804</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.612530430026347</v>
+        <v>0.778304739380306</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5956109501872024</v>
+        <v>0.7920791411799146</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6205780164245105</v>
+        <v>0.7872998936875029</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6205780164245105</v>
+        <v>0.8329218217956027</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6181060582715745</v>
+        <v>0.8125828158944888</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6043316564719659</v>
+        <v>0.808641357102137</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.610538996656549</v>
+        <v>0.8569962097283639</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5935097376084311</v>
+        <v>0.8480559450256537</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5889365668767237</v>
+        <v>0.852629115757361</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5639695006394158</v>
+        <v>0.852629115757361</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5670182811272206</v>
+        <v>0.8866876338535969</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5850499976888588</v>
+        <v>0.8909863565628707</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5990853658536586</v>
+        <v>0.8958753832642559</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6051829268292683</v>
+        <v>0.8795876153644671</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6164304808714542</v>
+        <v>0.8734900543888573</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6582207293961758</v>
+        <v>0.7535023419564582</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5664414587923516</v>
+        <v>0.7528706300171024</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5167682926829268</v>
+        <v>0.7480913825246907</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.524390243902439</v>
+        <v>0.7940291666024684</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5499890220791027</v>
+        <v>0.7964462351509175</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5255987781766637</v>
+        <v>0.7728523720012942</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.543891461103493</v>
+        <v>0.6997914195029505</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5335365853658537</v>
+        <v>0.7028401999907554</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5195012172010539</v>
+        <v>0.7028401999907554</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5076219512195121</v>
+        <v>0.6490743879327612</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5076219512195121</v>
+        <v>0.6490743879327612</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5060975609756098</v>
+        <v>0.5807926829268293</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5036256028226738</v>
+        <v>0.5884146341463414</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5051499930665763</v>
+        <v>0.5884146341463414</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5103548757376393</v>
+        <v>0.5884146341463414</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5088304854937368</v>
+        <v>0.5640243902439024</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5088304854937368</v>
+        <v>0.5701219512195121</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5292243809993374</v>
+        <v>0.6173780487804879</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5295402369690153</v>
+        <v>0.5396341463414634</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5602890082122551</v>
+        <v>0.5411585365853658</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5572402277244504</v>
+        <v>0.5320121951219512</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5453609617429087</v>
+        <v>0.5320121951219512</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5453609617429087</v>
+        <v>0.5304878048780488</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7465669922807883</v>
+        <v>0.5198170731707317</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6391865553210175</v>
+        <v>0.5182926829268293</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.627829222069858</v>
+        <v>0.5167682926829268</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6655682325932546</v>
+        <v>0.524390243902439</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7999620587646179</v>
+        <v>0.5320121951219512</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8133657149900622</v>
+        <v>0.5396341463414634</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7877813814461581</v>
+        <v>0.5564024390243902</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8167313144230621</v>
+        <v>0.5396341463414634</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8552118160947876</v>
+        <v>0.5259146341463414</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8552118160947876</v>
+        <v>0.5259146341463414</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8555276720644653</v>
+        <v>0.5167682926829268</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8125423709227617</v>
+        <v>0.5167682926829268</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7332191886353482</v>
+        <v>0.5213414634146342</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7570056468884335</v>
+        <v>0.5121951219512195</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7971212809885522</v>
+        <v>0.5198170731707317</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7361177449424525</v>
+        <v>0.5282768130903039</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7430530946181224</v>
+        <v>0.547874327843089</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7430530946181224</v>
+        <v>0.5485060397824446</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6462056838666934</v>
+        <v>0.5522963114185785</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6449422599879822</v>
+        <v>0.5502499884442938</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5769484846617259</v>
+        <v>0.5487255982003914</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5794753324191486</v>
+        <v>0.5572951173289371</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5292937152365839</v>
+        <v>0.5457317073170732</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4965400289663036</v>
+        <v>0.5362695098839807</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5043815386037626</v>
+        <v>0.5359536539143029</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.571551006887201</v>
+        <v>0.5359536539143029</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5451279216677195</v>
+        <v>0.5259146341463414</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5451279216677195</v>
+        <v>0.510670731707317</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4993682880606444</v>
+        <v>0.5137195121951219</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4993682880606444</v>
+        <v>0.5137195121951219</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5228658536585366</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5045731707317073</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4987365761212887</v>
+        <v>0.5030487804878049</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4990524320909665</v>
+        <v>0.5030487804878049</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4964158051245705</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5042438331047872</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5042438331047872</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
